--- a/business_registration_forms/034_color_street_wish_list--business_registration_forms.xlsx
+++ b/business_registration_forms/034_color_street_wish_list--business_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-- Your Color Street Wish List --</t>
+          <t>Your Wish List</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>wish_name</t>
+          <t>user_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>User Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -566,35 +566,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wish_email</t>
+          <t>wish_sets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>Your Top Wishes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>section_wishes</t>
+          <t>wish_sets_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-- My Top Wishes --</t>
+          <t>Another Set</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,24 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wish_set_1</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wish Set</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Name of the set you want most</t>
-        </is>
-      </c>
+          <t>Notify on Stock</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -634,20 +630,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wish_set_2</t>
+          <t>birthday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wish Set</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Birthday Month</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>I might send a gift!</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -662,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wish_set_3</t>
+          <t>additional_wishes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wish Set</t>
+          <t>Additional Wishes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wish_set_4</t>
+          <t>other_sets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wish Set</t>
+          <t>Other Sets</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wish_set_5</t>
+          <t>other_styles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wish Set</t>
+          <t>Other Styles</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,23 +726,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>notify_on_stock</t>
+          <t>other_wishes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Notify me if these come back in stock?</t>
+          <t>Other Wishes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -754,42 +754,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>birthday_month</t>
+          <t>notify_on_stock_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Your Birthday Month</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>I might send a special gift!</t>
-        </is>
-      </c>
+          <t>Notify me on Stock</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>additional_wishes</t>
+          <t>birthday_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Any other sets or styles you're looking for?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Another Birthday</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>I might send a gift!</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -807,10 +807,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -835,7 +835,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>notify_on_stock_choices</t>
+          <t>notification_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>notify_on_stock_choices</t>
+          <t>notification_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -886,7 +886,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -988,7 +988,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1022,7 +1022,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>birthday_month_choices</t>
+          <t>birthday_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1065,6 +1065,244 @@
         </is>
       </c>
       <c r="C15" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>notify_on_stock_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>notify_on_stock_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>january</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>february</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>march</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>april</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>june</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>august</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>september</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>october</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>november</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>birthday_2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>december</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>December</t>
         </is>
